--- a/branches/feat/tf-kds-brand-round2/StructureDefinition-example-patient.xlsx
+++ b/branches/feat/tf-kds-brand-round2/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T07:36:22+00:00</t>
+    <t>2026-08-14T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
